--- a/tools/python/temu-product-sheet/data/size_specs.xlsx
+++ b/tools/python/temu-product-sheet/data/size_specs.xlsx
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="141">
   <si>
     <t>宽度（cm）</t>
   </si>
@@ -184,37 +184,76 @@
     <t>41-45</t>
   </si>
   <si>
-    <t>65-70</t>
-  </si>
-  <si>
-    <t>3.1-3.3</t>
-  </si>
-  <si>
-    <t>170-175</t>
+    <t>39-46</t>
+  </si>
+  <si>
+    <t>60-71</t>
+  </si>
+  <si>
+    <t>2.35-2.5</t>
+  </si>
+  <si>
+    <t>120-130</t>
   </si>
   <si>
     <t>18-20</t>
   </si>
   <si>
-    <t>140-160</t>
-  </si>
-  <si>
-    <t>3.3-3.5</t>
-  </si>
-  <si>
-    <t>230-240</t>
-  </si>
-  <si>
-    <t>36-41</t>
-  </si>
-  <si>
-    <t>240-260</t>
-  </si>
-  <si>
-    <t>290-300</t>
-  </si>
-  <si>
-    <t>60-65</t>
+    <t>89-101</t>
+  </si>
+  <si>
+    <t>2.51-2.79</t>
+  </si>
+  <si>
+    <t>170-190</t>
+  </si>
+  <si>
+    <t>119-131</t>
+  </si>
+  <si>
+    <t>2.8-3.1</t>
+  </si>
+  <si>
+    <t>210-235</t>
+  </si>
+  <si>
+    <t>36-45</t>
+  </si>
+  <si>
+    <t>140-161</t>
+  </si>
+  <si>
+    <t>3.11-3.29</t>
+  </si>
+  <si>
+    <t>270-290</t>
+  </si>
+  <si>
+    <t>40-55</t>
+  </si>
+  <si>
+    <t>205-221</t>
+  </si>
+  <si>
+    <t>3.51-3.8</t>
+  </si>
+  <si>
+    <t>375-395</t>
+  </si>
+  <si>
+    <t>50-65</t>
+  </si>
+  <si>
+    <t>240-261</t>
+  </si>
+  <si>
+    <t>3.9-4.19</t>
+  </si>
+  <si>
+    <t>450-470</t>
+  </si>
+  <si>
+    <t>65-75</t>
   </si>
   <si>
     <t>商品编号</t>
@@ -1629,7 +1668,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="12" style="5" customWidth="1"/>
@@ -2471,53 +2510,53 @@
     </row>
     <row r="37" ht="18.75" spans="1:7">
       <c r="A37" s="25" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C37" s="25">
         <v>45</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F37" s="25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" ht="18.75" spans="1:7">
       <c r="A38" s="25" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C38" s="25">
         <v>45</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F38" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" ht="18.75" spans="1:7">
       <c r="A39" s="25" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B39" s="25" t="s">
         <v>50</v>
@@ -2526,16 +2565,85 @@
         <v>45</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E39" s="25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F39" s="25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" ht="18.75" spans="1:7">
+      <c r="A40" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="25">
+        <v>45</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="41" ht="18.75" spans="1:7">
+      <c r="A41" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="25">
+        <v>45</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F41" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="G41" s="25" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" ht="18.75" spans="1:7">
+      <c r="A42" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="25">
+        <v>45</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="G42" s="25" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -2560,33 +2668,33 @@
   <sheetData>
     <row r="1" ht="35" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:7">
       <c r="A2" s="6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C2" s="6">
         <v>1.1</v>
@@ -2606,10 +2714,10 @@
     </row>
     <row r="3" customFormat="1" ht="30" customHeight="1" spans="1:7">
       <c r="A3" s="6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C3" s="6">
         <v>2.1</v>
@@ -2629,10 +2737,10 @@
     </row>
     <row r="4" customFormat="1" ht="30" customHeight="1" spans="1:7">
       <c r="A4" s="6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C4" s="6">
         <v>1.1</v>
@@ -2652,10 +2760,10 @@
     </row>
     <row r="5" customFormat="1" ht="30" customHeight="1" spans="1:7">
       <c r="A5" s="6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C5" s="6">
         <v>1.1</v>
@@ -2696,359 +2804,359 @@
   <sheetData>
     <row r="1" ht="15" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
